--- a/data/source_data/Supplementary_TableS1_Figure1.xlsx
+++ b/data/source_data/Supplementary_TableS1_Figure1.xlsx
@@ -2,15 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MATLABコード\小論文用\Figure\SourceData_Workbooks\書き換えた論文の番号対応ソース\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{854B54B5-0ED6-41AB-B626-DC0B82C23C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB77987B-2779-4D47-8565-0C8032A3D2E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2268" yWindow="2268" windowWidth="17280" windowHeight="8820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-22140" yWindow="-8610" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TableS1_individual" sheetId="1" r:id="rId1"/>
@@ -260,7 +255,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="183" formatCode="0.000"/>
+    <numFmt numFmtId="176" formatCode="0.000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -302,7 +297,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="183" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
